--- a/data/merged/2026-09-23/MERGED_FR_Spot-Cleaner_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_FR_Spot-Cleaner_2026-09-23.xlsx
@@ -7006,50 +7006,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7391,7 +7347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -15046,40 +15002,40 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B07999DC2C</t>
+          <t>B0FS2B5W6P</t>
         </is>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Bissell</t>
+          <t>LEHMANN</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B07999DC2C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Bissell Brosse pour Taches Tenaces, Noir, 15 cm</t>
+          <t>LEHMANN EasyWash Shampouineuse Canapé 2 en 1, Nettoyage Puissant pour Taches Résistantes, Doppio Serbatoio, Nettoyeur Canapé,</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B07999DC2C?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FS2B5W6P?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61aI3+gXJwL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51ZfyHUDyDL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B07999DC2C</t>
+          <t>B0FS2B5W6P</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -15093,34 +15049,32 @@
         </is>
       </c>
       <c r="O34" s="15">
-        <v>4391</v>
+        <v>21274</v>
       </c>
       <c r="P34" s="15">
-        <v>-27</v>
+        <v>3499</v>
       </c>
       <c r="Q34" s="16">
-        <v>-0.01</v>
+        <v>0.31</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
-          <t>Accessoires pour nettoyeurs vapeur
-Nettoyeurs tapis et moquettes</t>
+          <t>Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>16
-23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T34" s="15">
-        <v>383</v>
+        <v>118</v>
       </c>
       <c r="U34" s="16">
-        <v>0.24</v>
+        <v>3.05</v>
       </c>
       <c r="V34" s="15">
-        <v>9571</v>
+        <v>9439</v>
       </c>
       <c r="W34" s="15" t="inlineStr">
         <is>
@@ -15128,78 +15082,84 @@
         </is>
       </c>
       <c r="X34" s="15">
-        <v>1323</v>
+        <v>3681</v>
       </c>
       <c r="Y34" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z34" s="20">
-        <v>20.82</v>
+        <v>79.99</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
-      <c r="AC34" s="2">
-        <v>4</v>
-      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" s="19">
-        <v>1384</v>
+        <v>62</v>
       </c>
       <c r="AE34" s="15">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AF34" s="21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AG34" s="22">
-        <v>0.0392</v>
+        <v>0.1864</v>
       </c>
       <c r="AH34" s="20">
-        <v>5.15</v>
+        <v>8.89</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>3036</v>
+        <v>304</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN34" s="13"/>
       <c r="AO34" s="13"/>
       <c r="AP34"/>
       <c r="AQ34" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR34" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU34" s="13"/>
-      <c r="AV34" s="14"/>
-      <c r="AW34" s="13"/>
-      <c r="AX34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU34" s="13" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="AV34" s="14" t="inlineStr">
+        <is>
+          <t>Greater Poland 63-100 PL</t>
+        </is>
+      </c>
+      <c r="AW34" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+        </is>
+      </c>
+      <c r="AX34" s="13"/>
       <c r="AY34" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15213,11 +15173,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD34" s="13"/>
       <c r="BE34" s="13"/>
       <c r="BF34" s="13"/>
       <c r="BG34" s="13"/>
@@ -15229,47 +15185,43 @@
       </c>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>137 g</t>
+          <t>4,5 Kilograms</t>
         </is>
       </c>
       <c r="BK34" s="23" t="inlineStr">
         <is>
-          <t>137.00 g</t>
+          <t>4.50 kg</t>
         </is>
       </c>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>40 x 25 x 15 cm</t>
-        </is>
-      </c>
-      <c r="BM34" s="23" t="inlineStr">
-        <is>
-          <t>40.00 x 25.00 x 15.00 cm</t>
-        </is>
-      </c>
+          <t>31,5P x 24l x 35,5H centimètres</t>
+        </is>
+      </c>
+      <c r="BM34" s="23"/>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>5.66 kg</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>150.00 g</t>
+          <t>5.66 kg</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>16.5 x 15 x 7.3 cm</t>
+          <t>38 x 36.2 x 26.2 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>16.50 x 15.00 x 7.30 cm</t>
+          <t>38.00 x 36.20 x 26.20 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -15280,127 +15232,125 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0FS2B5W6P</t>
+          <t>B0C3VKT151</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN</t>
+          <t>SUPER CLEAN</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN EasyWash Shampouineuse Canapé 2 en 1, Nettoyage Puissant pour Taches Résistantes, Doppio Serbatoio, Nettoyeur Canapé,</t>
+          <t>SUPER CLEAN Nettoyant concentré tapis et tissus nettoyage en profondeur adapté aux tapis sièges auto canapés contenu 2 x 500</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FS2B5W6P?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0C3VKT151?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51ZfyHUDyDL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41xcF1ROXCL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0FS2B5W6P</t>
+          <t>B0C3VKT151</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
+          <t>Cuisine et Maison:Produits et accessoires de nettoyage:Produits d'entretien:Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
+          <t>Voir les 100 premiers en Epicerie</t>
         </is>
       </c>
       <c r="O35" s="15">
-        <v>21274</v>
+        <v>1567</v>
       </c>
       <c r="P35" s="15">
-        <v>3499</v>
+        <v>22</v>
       </c>
       <c r="Q35" s="16">
-        <v>0.31</v>
+        <v>0.01</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
-          <t>Nettoyeurs tapis et moquettes</t>
+          <t>Nettoyants pour tapis de maison
+Produits d’entretien ménagers</t>
         </is>
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7
+199</t>
         </is>
       </c>
       <c r="T35" s="15">
-        <v>118</v>
+        <v>325</v>
       </c>
       <c r="U35" s="16">
-        <v>3.05</v>
+        <v>0.19</v>
       </c>
       <c r="V35" s="15">
-        <v>9439</v>
-      </c>
-      <c r="W35" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X35" s="15">
-        <v>3681</v>
-      </c>
+        <v>9308</v>
+      </c>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
       <c r="Y35" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z35" s="20">
-        <v>79.99</v>
+        <v>28.64</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
-      <c r="AC35" s="2"/>
+      <c r="AC35" s="2">
+        <v>26</v>
+      </c>
       <c r="AD35" s="19">
-        <v>62</v>
+        <v>8993</v>
       </c>
       <c r="AE35" s="15">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="AF35" s="21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG35" s="22">
-        <v>0.1864</v>
+        <v>0.2523</v>
       </c>
       <c r="AH35" s="20">
-        <v>8.89</v>
+        <v>5.96</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>304</v>
+        <v>1168</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN35" s="13"/>
@@ -15410,39 +15360,35 @@
         <v>10</v>
       </c>
       <c r="AR35" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>Innochem</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU35" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="AV35" s="14" t="inlineStr">
         <is>
-          <t>Greater Poland 63-100 PL</t>
+          <t>Teningen 79331 DE</t>
         </is>
       </c>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F</t>
         </is>
       </c>
       <c r="AX35" s="13"/>
-      <c r="AY35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY35" s="13"/>
       <c r="AZ35" s="13"/>
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
@@ -15451,55 +15397,59 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD35" s="13"/>
+      <c r="BD35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE35" s="13"/>
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
       <c r="BH35" s="14"/>
-      <c r="BI35" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI35" s="23"/>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>4,5 Kilograms</t>
+          <t>250 grammes</t>
         </is>
       </c>
       <c r="BK35" s="23" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>250.00 g</t>
         </is>
       </c>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>31,5P x 24l x 35,5H centimètres</t>
-        </is>
-      </c>
-      <c r="BM35" s="23"/>
+          <t>19,5 x 18,1 x 7,3 cm</t>
+        </is>
+      </c>
+      <c r="BM35" s="23" t="inlineStr">
+        <is>
+          <t>19.50 x 18.10 x 7.30 cm</t>
+        </is>
+      </c>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>5.66 kg</t>
+          <t>1.11 kg</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>5.66 kg</t>
+          <t>1.11 kg</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>38 x 36.2 x 26.2 cm</t>
+          <t>19.5 x 18.1 x 7.3 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>38.00 x 36.20 x 26.20 cm</t>
+          <t>19.50 x 18.10 x 7.30 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -15510,121 +15460,123 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0C3VKT151</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>SUPER CLEAN</t>
+          <t>Livatro</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN</t>
+          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>SUPER CLEAN Nettoyant concentré tapis et tissus nettoyage en profondeur adapté aux tapis sièges auto canapés contenu 2 x 500</t>
+          <t>Livatro Shampouineuse Canapé avec Grand Réservoir pour Tissus et TapissEau propre 2,3 L, eau sale 1,3 L pour nettoyer plus</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0C3VKT151?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FH4QL9GN?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41xcF1ROXCL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41OIdOf0WOL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0C3VKT151</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>Cuisine et Maison:Produits et accessoires de nettoyage:Produits d'entretien:Nettoyeurs tapis et moquettes</t>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="N36" s="14" t="inlineStr">
         <is>
-          <t>Voir les 100 premiers en Epicerie</t>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
         </is>
       </c>
       <c r="O36" s="15">
-        <v>1567</v>
+        <v>28762</v>
       </c>
       <c r="P36" s="15">
-        <v>22</v>
+        <v>10211</v>
       </c>
       <c r="Q36" s="16">
-        <v>0.01</v>
+        <v>0.25</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
-          <t>Nettoyants pour tapis de maison
-Produits d’entretien ménagers</t>
+          <t>Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>7
-199</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T36" s="15">
-        <v>325</v>
+        <v>97</v>
       </c>
       <c r="U36" s="16">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="V36" s="15">
-        <v>9308</v>
-      </c>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
+        <v>7001</v>
+      </c>
+      <c r="W36" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X36" s="15">
+        <v>3856</v>
+      </c>
       <c r="Y36" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z36" s="20">
-        <v>28.64</v>
+        <v>72.18</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
-      <c r="AC36" s="2">
-        <v>26</v>
-      </c>
+      <c r="AC36" s="2"/>
       <c r="AD36" s="19">
-        <v>8993</v>
+        <v>325</v>
       </c>
       <c r="AE36" s="15">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="AF36" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG36" s="22">
-        <v>0.2523</v>
+        <v>0.1959</v>
       </c>
       <c r="AH36" s="20">
-        <v>5.96</v>
+        <v>8.68</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>1168</v>
+        <v>393</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
@@ -15638,11 +15590,11 @@
         <v>10</v>
       </c>
       <c r="AR36" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>Innochem</t>
+          <t>Kayon International</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
@@ -15652,21 +15604,25 @@
       </c>
       <c r="AU36" s="13" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV36" s="14" t="inlineStr">
         <is>
-          <t>Teningen 79331 DE</t>
+          <t>HONGKONG 999077 HK</t>
         </is>
       </c>
       <c r="AW36" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B</t>
         </is>
       </c>
       <c r="AX36" s="13"/>
-      <c r="AY36" s="13"/>
+      <c r="AY36" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ36" s="13"/>
       <c r="BA36" s="13"/>
       <c r="BB36" s="13"/>
@@ -15684,50 +15640,50 @@
       <c r="BF36" s="13"/>
       <c r="BG36" s="13"/>
       <c r="BH36" s="14"/>
-      <c r="BI36" s="23"/>
+      <c r="BI36" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>250 grammes</t>
+          <t>3,8 Kilograms</t>
         </is>
       </c>
       <c r="BK36" s="23" t="inlineStr">
         <is>
-          <t>250.00 g</t>
+          <t>3.80 kg</t>
         </is>
       </c>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>19,5 x 18,1 x 7,3 cm</t>
-        </is>
-      </c>
-      <c r="BM36" s="23" t="inlineStr">
-        <is>
-          <t>19.50 x 18.10 x 7.30 cm</t>
-        </is>
-      </c>
+          <t>22,9P x 37l x 35,6H centimètres</t>
+        </is>
+      </c>
+      <c r="BM36" s="23"/>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>1.11 kg</t>
+          <t>4.66 kg</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>1.11 kg</t>
+          <t>4.66 kg</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>19.5 x 18.1 x 7.3 cm</t>
+          <t>45.1 x 36.6 x 20.5 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>19.50 x 18.10 x 7.30 cm</t>
+          <t>45.10 x 36.60 x 20.50 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -15738,40 +15694,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B08KXVXC82</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>Livatro</t>
+          <t>MEDION</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Livatro Shampouineuse Canapé avec Grand Réservoir pour Tissus et TapissEau propre 2,3 L, eau sale 1,3 L pour nettoyer plus</t>
+          <t>MEDION E10 UC Nettoyeur textile injecteur extracteur - 750 WsAspirateur eau pour tissus tapis sièges auto, réservoirs propr</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FH4QL9GN?psc=1</t>
+          <t>https://www.amazon.fr/dp/B08KXVXC82?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41OIdOf0WOL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41+Q-FdsUUL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B08KXVXC82</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -15785,13 +15741,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>28762</v>
+        <v>37213</v>
       </c>
       <c r="P37" s="15">
-        <v>10211</v>
+        <v>-1956</v>
       </c>
       <c r="Q37" s="16">
-        <v>0.25</v>
+        <v>-0.04</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -15800,49 +15756,43 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="U37" s="16">
-        <v>0.08</v>
+        <v>1.78</v>
       </c>
       <c r="V37" s="15">
-        <v>7001</v>
-      </c>
-      <c r="W37" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X37" s="15">
-        <v>3856</v>
-      </c>
+        <v>6226</v>
+      </c>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
       <c r="Y37" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>72.18</v>
+        <v>69.95</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="19">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="AE37" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AF37" s="21">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AG37" s="22">
-        <v>0.1959</v>
+        <v>0.17980000000000002</v>
       </c>
       <c r="AH37" s="20">
-        <v>8.68</v>
+        <v>8.89</v>
       </c>
       <c r="AI37" s="16">
         <v>0.73</v>
@@ -15850,11 +15800,11 @@
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>393</v>
+        <v>150</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
@@ -15868,11 +15818,11 @@
         <v>10</v>
       </c>
       <c r="AR37" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>Kayon International</t>
+          <t>medionshop-deutschland</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
@@ -15882,25 +15832,21 @@
       </c>
       <c r="AU37" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="AV37" s="14" t="inlineStr">
         <is>
-          <t>HONGKONG 999077 HK</t>
+          <t>Essen 45307 DE</t>
         </is>
       </c>
       <c r="AW37" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N</t>
         </is>
       </c>
       <c r="AX37" s="13"/>
-      <c r="AY37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY37" s="13"/>
       <c r="AZ37" s="13"/>
       <c r="BA37" s="13"/>
       <c r="BB37" s="13"/>
@@ -15909,54 +15855,46 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD37" s="13"/>
       <c r="BE37" s="13"/>
       <c r="BF37" s="13"/>
       <c r="BG37" s="13"/>
       <c r="BH37" s="14"/>
-      <c r="BI37" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI37" s="23"/>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>3,8 Kilograms</t>
+          <t>4,5 Kilograms</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>3.80 kg</t>
+          <t>4.50 kg</t>
         </is>
       </c>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>22,9P x 37l x 35,6H centimètres</t>
+          <t>24P x 31,7l x 35H centimètres</t>
         </is>
       </c>
       <c r="BM37" s="23"/>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>4.66 kg</t>
+          <t>6.05 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>4.66 kg</t>
+          <t>6.05 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>45.1 x 36.6 x 20.5 cm</t>
+          <t>37.6 x 37.1 x 26.9 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>45.10 x 36.60 x 20.50 cm</t>
+          <t>37.60 x 37.10 x 26.90 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
@@ -15972,40 +15910,40 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B08KXVXC82</t>
+          <t>B01HZUX61M</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>MEDION</t>
+          <t>Tech'N'Fast</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>MEDION E10 UC Nettoyeur textile injecteur extracteur - 750 WsAspirateur eau pour tissus tapis sièges auto, réservoirs propr</t>
+          <t>Nettoyant textile concentré, canapé, moquette, tapis, sièges auto, détachant, dissout les tâches et neutralise les odeurs - B</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B08KXVXC82?psc=1</t>
+          <t>https://www.amazon.fr/dp/B01HZUX61M?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41+Q-FdsUUL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51k6bvKW11L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B08KXVXC82</t>
+          <t>B01HZUX61M</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -16019,13 +15957,13 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>37213</v>
+        <v>10990</v>
       </c>
       <c r="P38" s="15">
-        <v>-1956</v>
+        <v>-4018</v>
       </c>
       <c r="Q38" s="16">
-        <v>-0.04</v>
+        <v>-0.58</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -16034,59 +15972,65 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="U38" s="16">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="V38" s="15">
-        <v>6226</v>
-      </c>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
+        <v>5964</v>
+      </c>
+      <c r="W38" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X38" s="15">
+        <v>3416</v>
+      </c>
       <c r="Y38" s="19">
         <v>1</v>
       </c>
       <c r="Z38" s="20">
-        <v>69.95</v>
+        <v>28.4</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="19">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="AE38" s="15">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AF38" s="21">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG38" s="22">
-        <v>0.17980000000000002</v>
+        <v>0.0333</v>
       </c>
       <c r="AH38" s="20">
-        <v>8.89</v>
+        <v>11.12</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2017-12-18</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>150</v>
+        <v>3200</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN38" s="13"/>
@@ -16100,27 +16044,27 @@
       </c>
       <c r="AS38" s="14" t="inlineStr">
         <is>
-          <t>medionshop-deutschland</t>
+          <t>DistriPro</t>
         </is>
       </c>
       <c r="AT38" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU38" s="13" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="AV38" s="14" t="inlineStr">
         <is>
-          <t>Essen 45307 DE</t>
+          <t>Grisy Suisnes 77166 FR</t>
         </is>
       </c>
       <c r="AW38" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA</t>
         </is>
       </c>
       <c r="AX38" s="13"/>
@@ -16133,7 +16077,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD38" s="13"/>
+      <c r="BD38" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE38" s="13"/>
       <c r="BF38" s="13"/>
       <c r="BG38" s="13"/>
@@ -16141,45 +16089,37 @@
       <c r="BI38" s="23"/>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>4,5 Kilograms</t>
+          <t>200 grammes</t>
         </is>
       </c>
       <c r="BK38" s="23" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>200.00 g</t>
         </is>
       </c>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>24P x 31,7l x 35H centimètres</t>
-        </is>
-      </c>
-      <c r="BM38" s="23"/>
+          <t>18 x 14 x 25 cm</t>
+        </is>
+      </c>
+      <c r="BM38" s="23" t="inlineStr">
+        <is>
+          <t>18.00 x 14.00 x 25.00 cm</t>
+        </is>
+      </c>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>6.05 kg</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>6.05 kg</t>
-        </is>
-      </c>
-      <c r="BP38" s="23" t="inlineStr">
-        <is>
-          <t>37.6 x 37.1 x 26.9 cm</t>
-        </is>
-      </c>
-      <c r="BQ38" s="23" t="inlineStr">
-        <is>
-          <t>37.60 x 37.10 x 26.90 cm</t>
-        </is>
-      </c>
-      <c r="BR38" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+          <t>200.00 g</t>
+        </is>
+      </c>
+      <c r="BP38" s="23"/>
+      <c r="BQ38" s="23"/>
+      <c r="BR38" s="13"/>
     </row>
     <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
@@ -16188,40 +16128,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B01HZUX61M</t>
+          <t>B0GHQBM3W1</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Tech'N'Fast</t>
+          <t>SIMPLUS</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQBM3W1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Nettoyant textile concentré, canapé, moquette, tapis, sièges auto, détachant, dissout les tâches et neutralise les odeurs - B</t>
+          <t>SIMPLUS Shampouineuse Canapé avec Fonction Autonettoyante, BlancsAspiration 12kPa, Idéal pour Poils d’Animaux, Nettoyeur Ta</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B01HZUX61M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GHQBM3W1?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51k6bvKW11L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41d4NPDnU9L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B01HZUX61M</t>
+          <t>B0GHQBM3W1</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -16235,13 +16175,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>10990</v>
+        <v>40734</v>
       </c>
       <c r="P39" s="15">
-        <v>-4018</v>
+        <v>42270</v>
       </c>
       <c r="Q39" s="16">
-        <v>-0.58</v>
+        <v>0.51</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -16250,65 +16190,65 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="U39" s="16">
-        <v>1.9</v>
+        <v>0.97</v>
       </c>
       <c r="V39" s="15">
-        <v>5964</v>
+        <v>5809</v>
       </c>
       <c r="W39" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X39" s="15">
-        <v>3416</v>
+        <v>3482</v>
       </c>
       <c r="Y39" s="19">
         <v>1</v>
       </c>
       <c r="Z39" s="20">
-        <v>28.4</v>
+        <v>69.99</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="19">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AE39" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF39" s="21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AG39" s="22">
-        <v>0.0333</v>
+        <v>0.0482</v>
       </c>
       <c r="AH39" s="20">
-        <v>11.12</v>
+        <v>8.11</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2017-12-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>3200</v>
+        <v>161</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN39" s="13"/>
@@ -16322,31 +16262,35 @@
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>DistriPro</t>
+          <t>Simplus Official</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU39" s="13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV39" s="14" t="inlineStr">
         <is>
-          <t>Grisy Suisnes 77166 FR</t>
+          <t>HK 999077 HK</t>
         </is>
       </c>
       <c r="AW39" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A</t>
         </is>
       </c>
       <c r="AX39" s="13"/>
-      <c r="AY39" s="13"/>
+      <c r="AY39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ39" s="13"/>
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
@@ -16364,40 +16308,52 @@
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
       <c r="BH39" s="14"/>
-      <c r="BI39" s="23"/>
+      <c r="BI39" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>200 grammes</t>
+          <t>2,5 Kilograms</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>200.00 g</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>18 x 14 x 25 cm</t>
-        </is>
-      </c>
-      <c r="BM39" s="23" t="inlineStr">
-        <is>
-          <t>18.00 x 14.00 x 25.00 cm</t>
-        </is>
-      </c>
+          <t>32,5P x 19l x 34,5H centimètres</t>
+        </is>
+      </c>
+      <c r="BM39" s="23"/>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>3.29 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>200.00 g</t>
-        </is>
-      </c>
-      <c r="BP39" s="23"/>
-      <c r="BQ39" s="23"/>
-      <c r="BR39" s="13"/>
+          <t>3.29 kg</t>
+        </is>
+      </c>
+      <c r="BP39" s="23" t="inlineStr">
+        <is>
+          <t>35.1 x 33.9 x 19.5 cm</t>
+        </is>
+      </c>
+      <c r="BQ39" s="23" t="inlineStr">
+        <is>
+          <t>35.10 x 33.90 x 19.50 cm</t>
+        </is>
+      </c>
+      <c r="BR39" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
@@ -16406,40 +16362,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0GHQBM3W1</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQBM3W1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS Shampouineuse Canapé avec Fonction Autonettoyante, BlancsAspiration 12kPa, Idéal pour Poils d’Animaux, Nettoyeur Ta</t>
+          <t>HAUSHOF StainZapper Shampouineuse 400 W avec Double RéservoirsNettoyeur de Tapis, Réservoirs 1,1 L + 0,5 L, Tuyau 1,2 m, 2</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GHQBM3W1?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41d4NPDnU9L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41mvaF7mrKL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0GHQBM3W1</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -16453,13 +16409,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>40734</v>
+        <v>33414</v>
       </c>
       <c r="P40" s="15">
-        <v>42270</v>
+        <v>-10393</v>
       </c>
       <c r="Q40" s="16">
-        <v>0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -16468,26 +16424,20 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="U40" s="16">
-        <v>0.97</v>
+        <v>-0.08</v>
       </c>
       <c r="V40" s="15">
-        <v>5809</v>
-      </c>
-      <c r="W40" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X40" s="15">
-        <v>3482</v>
-      </c>
+        <v>5599</v>
+      </c>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
       <c r="Y40" s="19">
         <v>1</v>
       </c>
@@ -16498,19 +16448,19 @@
       <c r="AB40"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="19">
-        <v>46</v>
+        <v>4834</v>
       </c>
       <c r="AE40" s="15">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="AF40" s="21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AG40" s="22">
-        <v>0.0482</v>
+        <v>0.5125</v>
       </c>
       <c r="AH40" s="20">
-        <v>8.11</v>
+        <v>8.47</v>
       </c>
       <c r="AI40" s="16">
         <v>0.73</v>
@@ -16518,15 +16468,15 @@
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>161</v>
+        <v>1253</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN40" s="13"/>
@@ -16536,33 +16486,21 @@
         <v>10</v>
       </c>
       <c r="AR40" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>Simplus Official</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU40" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV40" s="14" t="inlineStr">
-        <is>
-          <t>HK 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW40" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU40" s="13"/>
+      <c r="AV40" s="14"/>
+      <c r="AW40" s="13"/>
       <c r="AX40" s="13"/>
       <c r="AY40" s="13" t="inlineStr">
         <is>
@@ -16593,43 +16531,43 @@
       </c>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>2,5 Kilograms</t>
+          <t>3,4 Kilograms</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>3.40 kg</t>
         </is>
       </c>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>32,5P x 19l x 34,5H centimètres</t>
+          <t>15P x 28,5l x 26,5H centimètres</t>
         </is>
       </c>
       <c r="BM40" s="23"/>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>3.29 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>3.29 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>35.1 x 33.9 x 19.5 cm</t>
+          <t>40.2 x 34.2 x 19.5 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>35.10 x 33.90 x 19.50 cm</t>
+          <t>40.20 x 34.20 x 19.50 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16640,40 +16578,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0HGQXFPQ5</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>FILINK</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/FILINK/page/94A9CA40-FEC8-4B21-87F0-31F7B464C5FB?lp_asin=B0HGQXFPQ5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Shampouineuse 400 W avec Double RéservoirsNettoyeur de Tapis, Réservoirs 1,1 L + 0,5 L, Tuyau 1,2 m, 2</t>
+          <t>FILINK Shampouineuse 600w - 15kPa Nettoyeur Canapé Tissu - Avec DétergentsShampouineuse Canapé Portable - Détacheur Nettoye</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HGQXFPQ5?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41mvaF7mrKL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41Mj1VdXtjL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0HGQXFPQ5</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16687,13 +16625,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>33414</v>
+        <v>21547</v>
       </c>
       <c r="P41" s="15">
-        <v>-10393</v>
+        <v>-12355</v>
       </c>
       <c r="Q41" s="16">
-        <v>-0.4</v>
+        <v>-1.43</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16702,17 +16640,15 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>80</v>
-      </c>
-      <c r="U41" s="16">
-        <v>-0.08</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="U41" s="16"/>
       <c r="V41" s="15">
-        <v>5599</v>
+        <v>4769</v>
       </c>
       <c r="W41" s="15"/>
       <c r="X41" s="15"/>
@@ -16720,71 +16656,79 @@
         <v>1</v>
       </c>
       <c r="Z41" s="20">
-        <v>69.99</v>
+        <v>89.99</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="19">
-        <v>4834</v>
+        <v>4</v>
       </c>
       <c r="AE41" s="15">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="AF41" s="21">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.5125</v>
+        <v>0.0189</v>
       </c>
       <c r="AH41" s="20">
-        <v>8.47</v>
+        <v>8.34</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>1253</v>
+        <v>15</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
       <c r="AO41" s="13"/>
       <c r="AP41"/>
       <c r="AQ41" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR41" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>ELYXIA LIMITED</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU41" s="13"/>
-      <c r="AV41" s="14"/>
-      <c r="AW41" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU41" s="13" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="AV41" s="14" t="inlineStr">
+        <is>
+          <t>DUBLIN D13 T672 IE</t>
+        </is>
+      </c>
+      <c r="AW41" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29CAQLJPC64E0</t>
+        </is>
+      </c>
       <c r="AX41" s="13"/>
-      <c r="AY41" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY41" s="13"/>
       <c r="AZ41" s="13"/>
       <c r="BA41" s="13"/>
       <c r="BB41" s="13"/>
@@ -16802,50 +16746,42 @@
       <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
       <c r="BH41" s="14"/>
-      <c r="BI41" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI41" s="23"/>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>3,4 Kilograms</t>
+          <t>4 Kilograms</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>3.40 kg</t>
-        </is>
-      </c>
-      <c r="BL41" s="23" t="inlineStr">
-        <is>
-          <t>15P x 28,5l x 26,5H centimètres</t>
-        </is>
-      </c>
+          <t>4.00 kg</t>
+        </is>
+      </c>
+      <c r="BL41" s="23"/>
       <c r="BM41" s="23"/>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>40.2 x 34.2 x 19.5 cm</t>
+          <t>39 x 34 x 19.5 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>40.20 x 34.20 x 19.50 cm</t>
+          <t>39.00 x 34.00 x 19.50 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16856,40 +16792,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0HGQXFPQ5</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>FILINK</t>
+          <t>Hearten</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/FILINK/page/94A9CA40-FEC8-4B21-87F0-31F7B464C5FB?lp_asin=B0HGQXFPQ5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>FILINK Shampouineuse 600w - 15kPa Nettoyeur Canapé Tissu - Avec DétergentsShampouineuse Canapé Portable - Détacheur Nettoye</t>
+          <t>Hearten Shampouineuse Canapé, Aspiration 22kPa, avec AutonettoyantsNettoyeur Canapé Tissu, Compact et Portable, 1.5L Réserv</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0HGQXFPQ5?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H263J8GJ?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41Mj1VdXtjL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0HGQXFPQ5</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -16903,13 +16839,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>21547</v>
+        <v>10045</v>
       </c>
       <c r="P42" s="15">
-        <v>-12355</v>
+        <v>17497</v>
       </c>
       <c r="Q42" s="16">
-        <v>-1.43</v>
+        <v>0.64</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -16918,15 +16854,15 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="U42" s="16"/>
       <c r="V42" s="15">
-        <v>4769</v>
+        <v>4586</v>
       </c>
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
@@ -16934,37 +16870,37 @@
         <v>1</v>
       </c>
       <c r="Z42" s="20">
-        <v>89.99</v>
+        <v>53.32</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="19">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE42" s="15">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AF42" s="21">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.0189</v>
+        <v>0.1628</v>
       </c>
       <c r="AH42" s="20">
-        <v>8.34</v>
+        <v>8.11</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
@@ -16975,14 +16911,14 @@
       <c r="AO42" s="13"/>
       <c r="AP42"/>
       <c r="AQ42" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR42" s="19">
         <v>1</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>ELYXIA LIMITED</t>
+          <t>Hearten Direct</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
@@ -16992,17 +16928,17 @@
       </c>
       <c r="AU42" s="13" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV42" s="14" t="inlineStr">
         <is>
-          <t>DUBLIN D13 T672 IE</t>
+          <t>Hong Kong 999077 HK</t>
         </is>
       </c>
       <c r="AW42" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29CAQLJPC64E0</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6</t>
         </is>
       </c>
       <c r="AX42" s="13"/>
@@ -17027,34 +16963,42 @@
       <c r="BI42" s="23"/>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>4 Kilograms</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
-        </is>
-      </c>
-      <c r="BL42" s="23"/>
-      <c r="BM42" s="23"/>
+          <t>2.50 kg</t>
+        </is>
+      </c>
+      <c r="BL42" s="23" t="inlineStr">
+        <is>
+          <t>23.2 x 29.9 x 17.3 cm</t>
+        </is>
+      </c>
+      <c r="BM42" s="23" t="inlineStr">
+        <is>
+          <t>23.20 x 29.90 x 17.30 cm</t>
+        </is>
+      </c>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>4 kg</t>
+          <t>3.34 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>3.34 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>39 x 34 x 19.5 cm</t>
+          <t>32.4 x 32.2 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>39.00 x 34.00 x 19.50 cm</t>
+          <t>32.40 x 32.20 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
@@ -17070,40 +17014,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0H263J8GJ</t>
+          <t>B0G8ZCQP4L</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>Hearten</t>
+          <t>ICARE</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/ICARE/page/52F75A79-66C1-4F02-BA42-17BE0BC627C1?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Hearten Shampouineuse Canapé, Aspiration 22kPa, avec AutonettoyantsNettoyeur Canapé Tissu, Compact et Portable, 1.5L Réserv</t>
+          <t>ICARE Shampouineuse 600w - 15kPa Nettoyeur Canapé Tissu - Avec DétergentsDétacheur Nettoyeur de Tache - Shampouineuse Canap</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H263J8GJ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0G8ZCQP4L?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/418+lTRmKWL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0H263J8GJ</t>
+          <t>B0G8ZCQP4L</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -17117,13 +17061,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>10045</v>
+        <v>36838</v>
       </c>
       <c r="P43" s="15">
-        <v>17497</v>
+        <v>96490</v>
       </c>
       <c r="Q43" s="16">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17132,15 +17076,15 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="U43" s="16"/>
       <c r="V43" s="15">
-        <v>4586</v>
+        <v>4499</v>
       </c>
       <c r="W43" s="15"/>
       <c r="X43" s="15"/>
@@ -17148,37 +17092,37 @@
         <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>53.32</v>
+        <v>74.99</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="19">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AE43" s="15">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.1628</v>
+        <v>0.35</v>
       </c>
       <c r="AH43" s="20">
-        <v>8.11</v>
+        <v>8.68</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
@@ -17189,14 +17133,14 @@
       <c r="AO43" s="13"/>
       <c r="AP43"/>
       <c r="AQ43" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR43" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>Hearten Direct</t>
+          <t>VIVARALimited</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
@@ -17206,17 +17150,17 @@
       </c>
       <c r="AU43" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="AV43" s="14" t="inlineStr">
         <is>
-          <t>Hong Kong 999077 HK</t>
+          <t>DUBLIN D01 KF30 IE</t>
         </is>
       </c>
       <c r="AW43" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3</t>
         </is>
       </c>
       <c r="AX43" s="13"/>
@@ -17241,47 +17185,43 @@
       <c r="BI43" s="23"/>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>5,33 Kilograms</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>5.33 kg</t>
         </is>
       </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>23.2 x 29.9 x 17.3 cm</t>
-        </is>
-      </c>
-      <c r="BM43" s="23" t="inlineStr">
-        <is>
-          <t>23.20 x 29.90 x 17.30 cm</t>
-        </is>
-      </c>
+          <t>39P x 19,5l x 34H centimètres</t>
+        </is>
+      </c>
+      <c r="BM43" s="23"/>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>3.34 kg</t>
+          <t>5.33 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>3.34 kg</t>
+          <t>5.33 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>32.4 x 32.2 x 19.4 cm</t>
+          <t>39.1 x 39 x 20.3 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>32.40 x 32.20 x 19.40 cm</t>
+          <t>39.10 x 39.00 x 20.30 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17292,40 +17232,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0G8ZCQP4L</t>
+          <t>B0GFCMB74J</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>ICARE</t>
+          <t>Aquavex Pro</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/ICARE/page/52F75A79-66C1-4F02-BA42-17BE0BC627C1?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Aquavex+Pro</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>ICARE Shampouineuse 600w - 15kPa Nettoyeur Canapé Tissu - Avec DétergentsDétacheur Nettoyeur de Tache - Shampouineuse Canap</t>
+          <t>AquavexPro™ Ultra – Nettoyeur Injecteur Extracteur 1850W - 4 en 1 - Eau Froide/Chaude 65 °C &amp; Vapeur 100 °C, Réservoirs 1.8L+</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0G8ZCQP4L?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GFCMB74J?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/418+lTRmKWL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61DetLWBdTL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0G8ZCQP4L</t>
+          <t>B0GFCMB74J</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17339,13 +17279,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>36838</v>
+        <v>57571</v>
       </c>
       <c r="P44" s="15">
-        <v>96490</v>
+        <v>198463</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17354,15 +17294,17 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>57</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>60</v>
-      </c>
-      <c r="U44" s="16"/>
+        <v>23</v>
+      </c>
+      <c r="U44" s="16">
+        <v>0.36</v>
+      </c>
       <c r="V44" s="15">
-        <v>4499</v>
+        <v>3908</v>
       </c>
       <c r="W44" s="15"/>
       <c r="X44" s="15"/>
@@ -17370,37 +17312,37 @@
         <v>1</v>
       </c>
       <c r="Z44" s="20">
-        <v>74.99</v>
+        <v>169.9</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="19">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AE44" s="15">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="AF44" s="21">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AG44" s="22">
-        <v>0.35</v>
+        <v>0.087</v>
       </c>
       <c r="AH44" s="20">
-        <v>8.68</v>
+        <v>9.32</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>143</v>
+        <v>251</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
@@ -17414,11 +17356,11 @@
         <v>9</v>
       </c>
       <c r="AR44" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>VIVARALimited</t>
+          <t>LanzShop</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
@@ -17428,17 +17370,17 @@
       </c>
       <c r="AU44" s="13" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="AV44" s="14" t="inlineStr">
         <is>
-          <t>DUBLIN D01 KF30 IE</t>
+          <t>Lyon 69001 FR</t>
         </is>
       </c>
       <c r="AW44" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2P4XC47MO0O14</t>
         </is>
       </c>
       <c r="AX44" s="13"/>
@@ -17446,16 +17388,8 @@
       <c r="AZ44" s="13"/>
       <c r="BA44" s="13"/>
       <c r="BB44" s="13"/>
-      <c r="BC44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC44" s="13"/>
+      <c r="BD44" s="13"/>
       <c r="BE44" s="13"/>
       <c r="BF44" s="13"/>
       <c r="BG44" s="13"/>
@@ -17463,38 +17397,42 @@
       <c r="BI44" s="23"/>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>5,33 Kilograms</t>
+          <t>7 Kilograms</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>5.33 kg</t>
+          <t>7.00 kg</t>
         </is>
       </c>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>39P x 19,5l x 34H centimètres</t>
-        </is>
-      </c>
-      <c r="BM44" s="23"/>
+          <t>25 x 28.5 x 33 cm</t>
+        </is>
+      </c>
+      <c r="BM44" s="23" t="inlineStr">
+        <is>
+          <t>25.00 x 28.50 x 33.00 cm</t>
+        </is>
+      </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>5.33 kg</t>
+          <t>7 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>5.33 kg</t>
+          <t>7.00 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>39.1 x 39 x 20.3 cm</t>
+          <t>41 x 39 x 29 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>39.10 x 39.00 x 20.30 cm</t>
+          <t>41.00 x 39.00 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
@@ -17510,40 +17448,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0GFCMB74J</t>
+          <t>B0HHNM96WW</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Aquavex Pro</t>
+          <t>Lubluelu</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Aquavex+Pro</t>
+          <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0HHNM96WW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>AquavexPro™ Ultra – Nettoyeur Injecteur Extracteur 1850W - 4 en 1 - Eau Froide/Chaude 65 °C &amp; Vapeur 100 °C, Réservoirs 1.8L+</t>
+          <t>Lubluelu Shampouineuse Canapé 22 kPa, 600 W, Nettoyeur Tapis PortablesAuto-Nettoyante et Portable, avec Long Tuyau pour Can</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GFCMB74J?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HHNM96WW?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61DetLWBdTL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71VvjQwJisL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0GFCMB74J</t>
+          <t>B0HHNM96WW</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17557,13 +17495,11 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>57571</v>
-      </c>
-      <c r="P45" s="15">
-        <v>198463</v>
-      </c>
+        <v>8147</v>
+      </c>
+      <c r="P45" s="15"/>
       <c r="Q45" s="16">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17572,17 +17508,15 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>23</v>
-      </c>
-      <c r="U45" s="16">
-        <v>0.36</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U45" s="16"/>
       <c r="V45" s="15">
-        <v>3908</v>
+        <v>1710</v>
       </c>
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
@@ -17590,132 +17524,136 @@
         <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>169.9</v>
+        <v>71.24</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="19">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AE45" s="15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.087</v>
+        <v>0</v>
       </c>
       <c r="AH45" s="20">
-        <v>9.32</v>
+        <v>8.97</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>251</v>
+        <v>15</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45"/>
       <c r="AQ45" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR45" s="19">
         <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>LanzShop</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU45" s="13" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="AV45" s="14" t="inlineStr">
-        <is>
-          <t>Lyon 69001 FR</t>
-        </is>
-      </c>
-      <c r="AW45" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2P4XC47MO0O14</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU45" s="13"/>
+      <c r="AV45" s="14"/>
+      <c r="AW45" s="13"/>
       <c r="AX45" s="13"/>
-      <c r="AY45" s="13"/>
+      <c r="AY45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
-      <c r="BC45" s="13"/>
-      <c r="BD45" s="13"/>
+      <c r="BC45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
       <c r="BH45" s="14"/>
-      <c r="BI45" s="23"/>
+      <c r="BI45" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>7 Kilograms</t>
+          <t>3 kg</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>7.00 kg</t>
+          <t>3.00 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>25 x 28.5 x 33 cm</t>
+          <t>15.2 x 35 x 32 cm</t>
         </is>
       </c>
       <c r="BM45" s="23" t="inlineStr">
         <is>
-          <t>25.00 x 28.50 x 33.00 cm</t>
+          <t>15.20 x 35.00 x 32.00 cm</t>
         </is>
       </c>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>7 kg</t>
+          <t>4.13 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>7.00 kg</t>
+          <t>4.13 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>41 x 39 x 29 cm</t>
+          <t>44.2 x 33.9 x 20 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>41.00 x 39.00 x 29.00 cm</t>
+          <t>44.20 x 33.90 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17726,214 +17664,104 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0HHNM96WW</t>
+          <t>B0CNXZH3R4</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu</t>
-        </is>
-      </c>
+      <c r="F46" s="14"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0HHNM96WW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.frundefined</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Shampouineuse Canapé 22 kPa, 600 W, Nettoyeur Tapis PortablesAuto-Nettoyante et Portable, avec Long Tuyau pour Can</t>
+          <t>SpotClean HydroSteam Pro - Détacheurs à eau</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0HHNM96WW?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0CNXZH3R4?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71VvjQwJisL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71+RtleMUbL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0HHNM96WW</t>
-        </is>
-      </c>
-      <c r="M46" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="N46" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O46" s="15">
-        <v>8147</v>
-      </c>
+          <t>B0CNXZH3R4</t>
+        </is>
+      </c>
+      <c r="M46" s="14"/>
+      <c r="N46" s="14"/>
+      <c r="O46" s="15"/>
       <c r="P46" s="15"/>
-      <c r="Q46" s="16">
-        <v>0</v>
-      </c>
-      <c r="R46" s="17" t="inlineStr">
-        <is>
-          <t>Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="S46" s="18" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="T46" s="15">
-        <v>24</v>
-      </c>
+      <c r="Q46" s="16"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="18"/>
+      <c r="T46" s="15"/>
       <c r="U46" s="16"/>
-      <c r="V46" s="15">
-        <v>1710</v>
-      </c>
+      <c r="V46" s="15"/>
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
-      <c r="Y46" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z46" s="20">
-        <v>71.24</v>
-      </c>
+      <c r="Y46" s="19"/>
+      <c r="Z46" s="20"/>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="19">
-        <v>19</v>
-      </c>
-      <c r="AE46" s="15">
-        <v>0</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AE46" s="15"/>
       <c r="AF46" s="21">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AG46" s="22">
         <v>0</v>
       </c>
-      <c r="AH46" s="20">
-        <v>8.97</v>
-      </c>
+      <c r="AH46" s="20"/>
       <c r="AI46" s="16">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="AJ46"/>
-      <c r="AK46" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AL46" s="19">
-        <v>15</v>
-      </c>
-      <c r="AM46" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AK46" s="13"/>
+      <c r="AL46" s="19"/>
+      <c r="AM46" s="13"/>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
-      <c r="AQ46" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR46" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS46" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT46" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AQ46" s="19"/>
+      <c r="AR46" s="19"/>
+      <c r="AS46" s="14"/>
+      <c r="AT46" s="13"/>
       <c r="AU46" s="13"/>
       <c r="AV46" s="14"/>
       <c r="AW46" s="13"/>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
-      <c r="BC46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC46" s="13"/>
+      <c r="BD46" s="13"/>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
-      <c r="BJ46" s="23" t="inlineStr">
-        <is>
-          <t>3 kg</t>
-        </is>
-      </c>
-      <c r="BK46" s="23" t="inlineStr">
-        <is>
-          <t>3.00 kg</t>
-        </is>
-      </c>
-      <c r="BL46" s="23" t="inlineStr">
-        <is>
-          <t>15.2 x 35 x 32 cm</t>
-        </is>
-      </c>
-      <c r="BM46" s="23" t="inlineStr">
-        <is>
-          <t>15.20 x 35.00 x 32.00 cm</t>
-        </is>
-      </c>
-      <c r="BN46" s="23" t="inlineStr">
-        <is>
-          <t>4.13 kg</t>
-        </is>
-      </c>
-      <c r="BO46" s="23" t="inlineStr">
-        <is>
-          <t>4.13 kg</t>
-        </is>
-      </c>
-      <c r="BP46" s="23" t="inlineStr">
-        <is>
-          <t>44.2 x 33.9 x 20 cm</t>
-        </is>
-      </c>
-      <c r="BQ46" s="23" t="inlineStr">
-        <is>
-          <t>44.20 x 33.90 x 20.00 cm</t>
-        </is>
-      </c>
-      <c r="BR46" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BI46" s="23"/>
+      <c r="BJ46" s="23"/>
+      <c r="BK46" s="23"/>
+      <c r="BL46" s="23"/>
+      <c r="BM46" s="23"/>
+      <c r="BN46" s="23"/>
+      <c r="BO46" s="23"/>
+      <c r="BP46" s="23"/>
+      <c r="BQ46" s="23"/>
+      <c r="BR46" s="13"/>
     </row>
     <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13">
@@ -17942,7 +17770,7 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0CNXZH3R4</t>
+          <t>B0GJZ2RTZG</t>
         </is>
       </c>
       <c r="D47" s="14"/>
@@ -17955,23 +17783,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>SpotClean HydroSteam Pro - Détacheurs à eau</t>
+          <t>HAUSHOF Nettoyeur de Tapis Sans Fil 24 V, Shampouineuse PortablesAspiration 13 kPa avec Moteur Brushless, pour Moquettes, C</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0CNXZH3R4?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GJZ2RTZG?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71+RtleMUbL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71ksa9lOkpL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0CNXZH3R4</t>
+          <t>B0GJZ2RTZG</t>
         </is>
       </c>
       <c r="M47" s="14"/>
@@ -17992,11 +17820,11 @@
       <c r="AB47"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="19">
-        <v>137</v>
+        <v>9</v>
       </c>
       <c r="AE47" s="15"/>
       <c r="AF47" s="21">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AG47" s="22">
         <v>0</v>
@@ -18048,7 +17876,7 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0GJZ2RTZG</t>
+          <t>B0H3B6H4TM</t>
         </is>
       </c>
       <c r="D48" s="14"/>
@@ -18061,23 +17889,23 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF Nettoyeur de Tapis Sans Fil 24 V, Shampouineuse PortablesAspiration 13 kPa avec Moteur Brushless, pour Moquettes, C</t>
+          <t>DREAME N20 Steam Nettoyeur précision portable pr tapis, vapeur 100 °Csaspir. 17 000Pa, lavage à 70 °C, nett. tissus/tapis/m</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GJZ2RTZG?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H3B6H4TM?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ksa9lOkpL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/717wj1QyrFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0GJZ2RTZG</t>
+          <t>B0H3B6H4TM</t>
         </is>
       </c>
       <c r="M48" s="14"/>
@@ -18093,17 +17921,15 @@
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
       <c r="Y48" s="19"/>
-      <c r="Z48" s="20"/>
+      <c r="Z48" s="20">
+        <v>124.17</v>
+      </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="2"/>
-      <c r="AD48" s="19">
-        <v>9</v>
-      </c>
+      <c r="AD48" s="19"/>
       <c r="AE48" s="15"/>
-      <c r="AF48" s="21">
-        <v>3.9</v>
-      </c>
+      <c r="AF48" s="21"/>
       <c r="AG48" s="22">
         <v>0</v>
       </c>
@@ -18154,7 +17980,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0H3B6H4TM</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -18167,23 +17993,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>DREAME N20 Steam Nettoyeur précision portable pr tapis, vapeur 100 °Csaspir. 17 000Pa, lavage à 70 °C, nett. tissus/tapis/m</t>
+          <t>LEHMANN SteamWash 1800 - Nettoyeur Vapeur 4 en 1 &amp; Aspirateur Injecteur Extracteur, Nettoyeur à Main Portable Canapé, Tapis,</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H3B6H4TM?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H3LCDNGF?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/717wj1QyrFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0H3B6H4TM</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="M49" s="14"/>
@@ -18199,15 +18025,17 @@
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
       <c r="Y49" s="19"/>
-      <c r="Z49" s="20">
-        <v>124.17</v>
-      </c>
+      <c r="Z49" s="20"/>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="2"/>
-      <c r="AD49" s="19"/>
+      <c r="AD49" s="19">
+        <v>36</v>
+      </c>
       <c r="AE49" s="15"/>
-      <c r="AF49" s="21"/>
+      <c r="AF49" s="21">
+        <v>4</v>
+      </c>
       <c r="AG49" s="22">
         <v>0</v>
       </c>
@@ -18258,7 +18086,7 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0HCN3FWXH</t>
         </is>
       </c>
       <c r="D50" s="14"/>
@@ -18271,23 +18099,23 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN SteamWash 1800 - Nettoyeur Vapeur 4 en 1 &amp; Aspirateur Injecteur Extracteur, Nettoyeur à Main Portable Canapé, Tapis,</t>
+          <t>TWOPOINT shampouineuse Puissante aspiration de 15 kPa, design léger et portable de seulement 3,8 kg, adapté aux tapis, canapé</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H3LCDNGF?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HCN3FWXH?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71Xqa1xYofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0HCN3FWXH</t>
         </is>
       </c>
       <c r="M50" s="14"/>
@@ -18308,11 +18136,11 @@
       <c r="AB50"/>
       <c r="AC50" s="2"/>
       <c r="AD50" s="19">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AE50" s="15"/>
       <c r="AF50" s="21">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AG50" s="22">
         <v>0</v>
@@ -18356,112 +18184,6 @@
       <c r="BP50" s="23"/>
       <c r="BQ50" s="23"/>
       <c r="BR50" s="13"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HCN3FWXH</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.frundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>TWOPOINT shampouineuse Puissante aspiration de 15 kPa, design léger et portable de seulement 3,8 kg, adapté aux tapis, canapé</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0HCN3FWXH?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71Xqa1xYofL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HCN3FWXH</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>8</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18702,134 +18424,127 @@
     <hyperlink ref="L33" r:id="rId233" tooltip="https://www.amazon.fr/dp/B0DSLQV39Z"/>
     <hyperlink ref="M33" r:id="rId234" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N33" r:id="rId235"/>
-    <hyperlink ref="C34" r:id="rId236" tooltip="https://www.amazon.fr/dp/B07999DC2C"/>
-    <hyperlink ref="G34" r:id="rId237" tooltip="https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B07999DC2C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J34" r:id="rId238" tooltip="https://www.amazon.fr/dp/B07999DC2C?psc=1"/>
-    <hyperlink ref="K34" r:id="rId239" tooltip="https://images-na.ssl-images-amazon.com/images/I/61aI3+gXJwL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId240" tooltip="https://www.amazon.fr/dp/B07999DC2C"/>
+    <hyperlink ref="C34" r:id="rId236" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
+    <hyperlink ref="G34" r:id="rId237" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J34" r:id="rId238" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P?psc=1"/>
+    <hyperlink ref="K34" r:id="rId239" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51ZfyHUDyDL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId240" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
     <hyperlink ref="M34" r:id="rId241" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N34" r:id="rId242"/>
-    <hyperlink ref="C35" r:id="rId243" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
-    <hyperlink ref="G35" r:id="rId244" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J35" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P?psc=1"/>
-    <hyperlink ref="K35" r:id="rId246" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51ZfyHUDyDL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId247" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
-    <hyperlink ref="M35" r:id="rId248" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N35" r:id="rId249"/>
-    <hyperlink ref="AW35" r:id="rId250" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C36" r:id="rId251" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
-    <hyperlink ref="G36" r:id="rId252" tooltip="https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN"/>
-    <hyperlink ref="J36" r:id="rId253" tooltip="https://www.amazon.fr/dp/B0C3VKT151?psc=1"/>
-    <hyperlink ref="K36" r:id="rId254" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41xcF1ROXCL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId255" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
-    <hyperlink ref="M36" r:id="rId256" tooltip="https://www.amazon.fr/b?node=3575161031"/>
-    <hyperlink ref="N36" r:id="rId257"/>
-    <hyperlink ref="AW36" r:id="rId258" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F"/>
-    <hyperlink ref="C37" r:id="rId259" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
-    <hyperlink ref="G37" r:id="rId260" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J37" r:id="rId261" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN?psc=1"/>
-    <hyperlink ref="K37" r:id="rId262" tooltip="https://m.media-amazon.com/images/I/41OIdOf0WOL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId263" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
-    <hyperlink ref="M37" r:id="rId264" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N37" r:id="rId265"/>
-    <hyperlink ref="AW37" r:id="rId266" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B"/>
-    <hyperlink ref="C38" r:id="rId267" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
-    <hyperlink ref="G38" r:id="rId268" tooltip="https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J38" r:id="rId269" tooltip="https://www.amazon.fr/dp/B08KXVXC82?psc=1"/>
-    <hyperlink ref="K38" r:id="rId270" tooltip="https://m.media-amazon.com/images/I/41+Q-FdsUUL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId271" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
-    <hyperlink ref="M38" r:id="rId272" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N38" r:id="rId273"/>
-    <hyperlink ref="AW38" r:id="rId274" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N"/>
-    <hyperlink ref="C39" r:id="rId275" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
-    <hyperlink ref="G39" r:id="rId276" tooltip="https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId277" tooltip="https://www.amazon.fr/dp/B01HZUX61M?psc=1"/>
-    <hyperlink ref="K39" r:id="rId278" tooltip="https://images-na.ssl-images-amazon.com/images/I/51k6bvKW11L._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId279" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
-    <hyperlink ref="M39" r:id="rId280" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N39" r:id="rId281"/>
-    <hyperlink ref="AW39" r:id="rId282" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA"/>
-    <hyperlink ref="C40" r:id="rId283" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
-    <hyperlink ref="G40" r:id="rId284" tooltip="https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQBM3W1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J40" r:id="rId285" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1?psc=1"/>
-    <hyperlink ref="K40" r:id="rId286" tooltip="https://m.media-amazon.com/images/I/41d4NPDnU9L._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId287" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
-    <hyperlink ref="M40" r:id="rId288" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N40" r:id="rId289"/>
-    <hyperlink ref="AW40" r:id="rId290" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A"/>
-    <hyperlink ref="C41" r:id="rId291" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
-    <hyperlink ref="G41" r:id="rId292" tooltip="https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId293" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1"/>
-    <hyperlink ref="K41" r:id="rId294" tooltip="https://m.media-amazon.com/images/I/41mvaF7mrKL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId295" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="AW34" r:id="rId243" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C35" r:id="rId244" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
+    <hyperlink ref="G35" r:id="rId245" tooltip="https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN"/>
+    <hyperlink ref="J35" r:id="rId246" tooltip="https://www.amazon.fr/dp/B0C3VKT151?psc=1"/>
+    <hyperlink ref="K35" r:id="rId247" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41xcF1ROXCL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId248" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
+    <hyperlink ref="M35" r:id="rId249" tooltip="https://www.amazon.fr/b?node=3575161031"/>
+    <hyperlink ref="N35" r:id="rId250"/>
+    <hyperlink ref="AW35" r:id="rId251" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F"/>
+    <hyperlink ref="C36" r:id="rId252" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
+    <hyperlink ref="G36" r:id="rId253" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J36" r:id="rId254" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN?psc=1"/>
+    <hyperlink ref="K36" r:id="rId255" tooltip="https://m.media-amazon.com/images/I/41OIdOf0WOL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId256" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
+    <hyperlink ref="M36" r:id="rId257" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N36" r:id="rId258"/>
+    <hyperlink ref="AW36" r:id="rId259" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B"/>
+    <hyperlink ref="C37" r:id="rId260" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
+    <hyperlink ref="G37" r:id="rId261" tooltip="https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J37" r:id="rId262" tooltip="https://www.amazon.fr/dp/B08KXVXC82?psc=1"/>
+    <hyperlink ref="K37" r:id="rId263" tooltip="https://m.media-amazon.com/images/I/41+Q-FdsUUL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId264" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
+    <hyperlink ref="M37" r:id="rId265" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N37" r:id="rId266"/>
+    <hyperlink ref="AW37" r:id="rId267" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N"/>
+    <hyperlink ref="C38" r:id="rId268" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
+    <hyperlink ref="G38" r:id="rId269" tooltip="https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId270" tooltip="https://www.amazon.fr/dp/B01HZUX61M?psc=1"/>
+    <hyperlink ref="K38" r:id="rId271" tooltip="https://images-na.ssl-images-amazon.com/images/I/51k6bvKW11L._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId272" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
+    <hyperlink ref="M38" r:id="rId273" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N38" r:id="rId274"/>
+    <hyperlink ref="AW38" r:id="rId275" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA"/>
+    <hyperlink ref="C39" r:id="rId276" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
+    <hyperlink ref="G39" r:id="rId277" tooltip="https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQBM3W1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J39" r:id="rId278" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1?psc=1"/>
+    <hyperlink ref="K39" r:id="rId279" tooltip="https://m.media-amazon.com/images/I/41d4NPDnU9L._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId280" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
+    <hyperlink ref="M39" r:id="rId281" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N39" r:id="rId282"/>
+    <hyperlink ref="AW39" r:id="rId283" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A"/>
+    <hyperlink ref="C40" r:id="rId284" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="G40" r:id="rId285" tooltip="https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J40" r:id="rId286" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1"/>
+    <hyperlink ref="K40" r:id="rId287" tooltip="https://m.media-amazon.com/images/I/41mvaF7mrKL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId288" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="M40" r:id="rId289" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N40" r:id="rId290"/>
+    <hyperlink ref="C41" r:id="rId291" tooltip="https://www.amazon.fr/dp/B0HGQXFPQ5"/>
+    <hyperlink ref="G41" r:id="rId292" tooltip="https://www.amazon.fr/stores/FILINK/page/94A9CA40-FEC8-4B21-87F0-31F7B464C5FB?lp_asin=B0HGQXFPQ5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J41" r:id="rId293" tooltip="https://www.amazon.fr/dp/B0HGQXFPQ5?psc=1"/>
+    <hyperlink ref="K41" r:id="rId294" tooltip="https://m.media-amazon.com/images/I/41Mj1VdXtjL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId295" tooltip="https://www.amazon.fr/dp/B0HGQXFPQ5"/>
     <hyperlink ref="M41" r:id="rId296" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N41" r:id="rId297"/>
-    <hyperlink ref="C42" r:id="rId298" tooltip="https://www.amazon.fr/dp/B0HGQXFPQ5"/>
-    <hyperlink ref="G42" r:id="rId299" tooltip="https://www.amazon.fr/stores/FILINK/page/94A9CA40-FEC8-4B21-87F0-31F7B464C5FB?lp_asin=B0HGQXFPQ5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J42" r:id="rId300" tooltip="https://www.amazon.fr/dp/B0HGQXFPQ5?psc=1"/>
-    <hyperlink ref="K42" r:id="rId301" tooltip="https://m.media-amazon.com/images/I/41Mj1VdXtjL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId302" tooltip="https://www.amazon.fr/dp/B0HGQXFPQ5"/>
-    <hyperlink ref="M42" r:id="rId303" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N42" r:id="rId304"/>
-    <hyperlink ref="AW42" r:id="rId305" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29CAQLJPC64E0"/>
-    <hyperlink ref="C43" r:id="rId306" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
-    <hyperlink ref="G43" r:id="rId307" tooltip="https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J43" r:id="rId308" tooltip="https://www.amazon.fr/dp/B0H263J8GJ?psc=1"/>
-    <hyperlink ref="K43" r:id="rId309" tooltip="https://images-na.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId310" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
-    <hyperlink ref="M43" r:id="rId311" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N43" r:id="rId312"/>
-    <hyperlink ref="AW43" r:id="rId313" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6"/>
-    <hyperlink ref="C44" r:id="rId314" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L"/>
-    <hyperlink ref="G44" r:id="rId315" tooltip="https://www.amazon.fr/stores/ICARE/page/52F75A79-66C1-4F02-BA42-17BE0BC627C1?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J44" r:id="rId316" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L?psc=1"/>
-    <hyperlink ref="K44" r:id="rId317" tooltip="https://m.media-amazon.com/images/I/418+lTRmKWL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId318" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L"/>
-    <hyperlink ref="M44" r:id="rId319" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N44" r:id="rId320"/>
-    <hyperlink ref="AW44" r:id="rId321" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3"/>
-    <hyperlink ref="C45" r:id="rId322" tooltip="https://www.amazon.fr/dp/B0GFCMB74J"/>
-    <hyperlink ref="G45" r:id="rId323" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Aquavex+Pro"/>
-    <hyperlink ref="J45" r:id="rId324" tooltip="https://www.amazon.fr/dp/B0GFCMB74J?psc=1"/>
-    <hyperlink ref="K45" r:id="rId325" tooltip="https://images-na.ssl-images-amazon.com/images/I/61DetLWBdTL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId326" tooltip="https://www.amazon.fr/dp/B0GFCMB74J"/>
-    <hyperlink ref="M45" r:id="rId327" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N45" r:id="rId328"/>
-    <hyperlink ref="AW45" r:id="rId329" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2P4XC47MO0O14"/>
-    <hyperlink ref="C46" r:id="rId330" tooltip="https://www.amazon.fr/dp/B0HHNM96WW"/>
-    <hyperlink ref="G46" r:id="rId331" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0HHNM96WW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId332" tooltip="https://www.amazon.fr/dp/B0HHNM96WW?psc=1"/>
-    <hyperlink ref="K46" r:id="rId333" tooltip="https://images-na.ssl-images-amazon.com/images/I/71VvjQwJisL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId334" tooltip="https://www.amazon.fr/dp/B0HHNM96WW"/>
-    <hyperlink ref="M46" r:id="rId335" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N46" r:id="rId336"/>
-    <hyperlink ref="C47" r:id="rId337" tooltip="https://www.amazon.fr/dp/B0CNXZH3R4"/>
-    <hyperlink ref="G47" r:id="rId338" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J47" r:id="rId339" tooltip="https://www.amazon.fr/dp/B0CNXZH3R4?psc=1"/>
-    <hyperlink ref="K47" r:id="rId340" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+RtleMUbL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId341" tooltip="https://www.amazon.fr/dp/B0CNXZH3R4"/>
-    <hyperlink ref="C48" r:id="rId342" tooltip="https://www.amazon.fr/dp/B0GJZ2RTZG"/>
-    <hyperlink ref="G48" r:id="rId343" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J48" r:id="rId344" tooltip="https://www.amazon.fr/dp/B0GJZ2RTZG?psc=1"/>
-    <hyperlink ref="K48" r:id="rId345" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ksa9lOkpL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId346" tooltip="https://www.amazon.fr/dp/B0GJZ2RTZG"/>
-    <hyperlink ref="C49" r:id="rId347" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM"/>
-    <hyperlink ref="G49" r:id="rId348" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J49" r:id="rId349" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM?psc=1"/>
-    <hyperlink ref="K49" r:id="rId350" tooltip="https://images-eu.ssl-images-amazon.com/images/I/717wj1QyrFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId351" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM"/>
-    <hyperlink ref="C50" r:id="rId352" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
-    <hyperlink ref="G50" r:id="rId353" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J50" r:id="rId354" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF?psc=1"/>
-    <hyperlink ref="K50" r:id="rId355" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId356" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
-    <hyperlink ref="C51" r:id="rId357" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH"/>
-    <hyperlink ref="G51" r:id="rId358" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J51" r:id="rId359" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH?psc=1"/>
-    <hyperlink ref="K51" r:id="rId360" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Xqa1xYofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId361" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH"/>
+    <hyperlink ref="AW41" r:id="rId298" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29CAQLJPC64E0"/>
+    <hyperlink ref="C42" r:id="rId299" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
+    <hyperlink ref="G42" r:id="rId300" tooltip="https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J42" r:id="rId301" tooltip="https://www.amazon.fr/dp/B0H263J8GJ?psc=1"/>
+    <hyperlink ref="K42" r:id="rId302" tooltip="https://images-na.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId303" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
+    <hyperlink ref="M42" r:id="rId304" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N42" r:id="rId305"/>
+    <hyperlink ref="AW42" r:id="rId306" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6"/>
+    <hyperlink ref="C43" r:id="rId307" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L"/>
+    <hyperlink ref="G43" r:id="rId308" tooltip="https://www.amazon.fr/stores/ICARE/page/52F75A79-66C1-4F02-BA42-17BE0BC627C1?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J43" r:id="rId309" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L?psc=1"/>
+    <hyperlink ref="K43" r:id="rId310" tooltip="https://m.media-amazon.com/images/I/418+lTRmKWL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId311" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L"/>
+    <hyperlink ref="M43" r:id="rId312" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N43" r:id="rId313"/>
+    <hyperlink ref="AW43" r:id="rId314" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3"/>
+    <hyperlink ref="C44" r:id="rId315" tooltip="https://www.amazon.fr/dp/B0GFCMB74J"/>
+    <hyperlink ref="G44" r:id="rId316" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Aquavex+Pro"/>
+    <hyperlink ref="J44" r:id="rId317" tooltip="https://www.amazon.fr/dp/B0GFCMB74J?psc=1"/>
+    <hyperlink ref="K44" r:id="rId318" tooltip="https://images-na.ssl-images-amazon.com/images/I/61DetLWBdTL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId319" tooltip="https://www.amazon.fr/dp/B0GFCMB74J"/>
+    <hyperlink ref="M44" r:id="rId320" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N44" r:id="rId321"/>
+    <hyperlink ref="AW44" r:id="rId322" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2P4XC47MO0O14"/>
+    <hyperlink ref="C45" r:id="rId323" tooltip="https://www.amazon.fr/dp/B0HHNM96WW"/>
+    <hyperlink ref="G45" r:id="rId324" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0HHNM96WW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId325" tooltip="https://www.amazon.fr/dp/B0HHNM96WW?psc=1"/>
+    <hyperlink ref="K45" r:id="rId326" tooltip="https://images-na.ssl-images-amazon.com/images/I/71VvjQwJisL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId327" tooltip="https://www.amazon.fr/dp/B0HHNM96WW"/>
+    <hyperlink ref="M45" r:id="rId328" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N45" r:id="rId329"/>
+    <hyperlink ref="C46" r:id="rId330" tooltip="https://www.amazon.fr/dp/B0CNXZH3R4"/>
+    <hyperlink ref="G46" r:id="rId331" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J46" r:id="rId332" tooltip="https://www.amazon.fr/dp/B0CNXZH3R4?psc=1"/>
+    <hyperlink ref="K46" r:id="rId333" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+RtleMUbL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId334" tooltip="https://www.amazon.fr/dp/B0CNXZH3R4"/>
+    <hyperlink ref="C47" r:id="rId335" tooltip="https://www.amazon.fr/dp/B0GJZ2RTZG"/>
+    <hyperlink ref="G47" r:id="rId336" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J47" r:id="rId337" tooltip="https://www.amazon.fr/dp/B0GJZ2RTZG?psc=1"/>
+    <hyperlink ref="K47" r:id="rId338" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ksa9lOkpL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId339" tooltip="https://www.amazon.fr/dp/B0GJZ2RTZG"/>
+    <hyperlink ref="C48" r:id="rId340" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM"/>
+    <hyperlink ref="G48" r:id="rId341" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J48" r:id="rId342" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM?psc=1"/>
+    <hyperlink ref="K48" r:id="rId343" tooltip="https://images-eu.ssl-images-amazon.com/images/I/717wj1QyrFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId344" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM"/>
+    <hyperlink ref="C49" r:id="rId345" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
+    <hyperlink ref="G49" r:id="rId346" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J49" r:id="rId347" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF?psc=1"/>
+    <hyperlink ref="K49" r:id="rId348" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId349" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
+    <hyperlink ref="C50" r:id="rId350" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH"/>
+    <hyperlink ref="G50" r:id="rId351" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J50" r:id="rId352" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH?psc=1"/>
+    <hyperlink ref="K50" r:id="rId353" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Xqa1xYofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId354" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH"/>
   </hyperlinks>
-  <drawing r:id="rId362"/>
+  <drawing r:id="rId355"/>
 </worksheet>
 </file>
 
@@ -18888,18 +18603,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>17287</v>
+        <v>16904</v>
       </c>
       <c r="C2" s="15">
-        <v>1142001</v>
+        <v>1132430</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>66.06125990628796</v>
+        <v>66.99183625177473</v>
       </c>
       <c r="G2" s="22">
-        <v>0.6770984293603854</v>
+        <v>0.672180690313345</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18920,7 +18635,7 @@
         <v>148.00413436692506</v>
       </c>
       <c r="G3" s="22">
-        <v>0.07579021581606674</v>
+        <v>0.07694448862732622</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18941,7 +18656,7 @@
         <v>222.915</v>
       </c>
       <c r="G4" s="22">
-        <v>0.023500842113509068</v>
+        <v>0.023858756163512008</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18962,7 +18677,7 @@
         <v>104.02098540145985</v>
       </c>
       <c r="G5" s="22">
-        <v>0.04292820492734323</v>
+        <v>0.04358199459201527</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18983,7 +18698,7 @@
         <v>55.24534803583735</v>
       </c>
       <c r="G6" s="22">
-        <v>0.05683286984450276</v>
+        <v>0.05769842532209321</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19004,7 +18719,7 @@
         <v>191.28947368421052</v>
       </c>
       <c r="G7" s="22">
-        <v>0.013395480004700169</v>
+        <v>0.013599491013201846</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19025,7 +18740,7 @@
         <v>133.31967213114754</v>
       </c>
       <c r="G8" s="22">
-        <v>0.01911401825232071</v>
+        <v>0.019405121679656433</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19046,7 +18761,7 @@
         <v>108.32</v>
       </c>
       <c r="G9" s="22">
-        <v>0.009792017547295445</v>
+        <v>0.009941148401463337</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19067,7 +18782,7 @@
         <v>199.99159663865547</v>
       </c>
       <c r="G10" s="22">
-        <v>0.004661000352512631</v>
+        <v>0.004731986639096549</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19088,7 +18803,7 @@
         <v>99.9020618556701</v>
       </c>
       <c r="G11" s="22">
-        <v>0.007598605616701265</v>
+        <v>0.007714331159535549</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19109,7 +18824,7 @@
         <v>91.85964912280701</v>
       </c>
       <c r="G12" s="22">
-        <v>0.006697740002350084</v>
+        <v>0.006799745506600923</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19130,7 +18845,7 @@
         <v>699.0</v>
       </c>
       <c r="G13" s="22">
-        <v>0.0008225294739728174</v>
+        <v>0.0008350564657229203</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19151,7 +18866,7 @@
         <v>60.160377358490564</v>
       </c>
       <c r="G14" s="22">
-        <v>0.008303630880106537</v>
+        <v>0.00843009384444091</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19172,7 +18887,7 @@
         <v>54.99</v>
       </c>
       <c r="G15" s="22">
-        <v>0.007833614037836356</v>
+        <v>0.00795291872117067</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19193,7 +18908,7 @@
         <v>79.99152542372882</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0046218322823234495</v>
+        <v>0.004692222045490695</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19214,7 +18929,7 @@
         <v>28.64</v>
       </c>
       <c r="G17" s="22">
-        <v>0.012729622811484077</v>
+        <v>0.012923492921902337</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19235,7 +18950,7 @@
         <v>72.17525773195877</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0037993028083506326</v>
+        <v>0.0038571655797677747</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19256,7 +18971,7 @@
         <v>69.95505617977528</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0034859582468371782</v>
+        <v>0.003539048830920948</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19277,7 +18992,7 @@
         <v>28.4</v>
       </c>
       <c r="G20" s="22">
-        <v>0.008225294739728174</v>
+        <v>0.008350564657229203</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19298,7 +19013,7 @@
         <v>69.9875</v>
       </c>
       <c r="G21" s="22">
-        <v>0.003133445615134542</v>
+        <v>0.003181167488468268</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19319,7 +19034,7 @@
         <v>89.98113207547169</v>
       </c>
       <c r="G22" s="22">
-        <v>0.0020759077200266343</v>
+        <v>0.0021075234611102273</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19340,7 +19055,7 @@
         <v>53.325581395348834</v>
       </c>
       <c r="G23" s="22">
-        <v>0.003368454036269633</v>
+        <v>0.003419755050103388</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19361,7 +19076,7 @@
         <v>74.98333333333333</v>
       </c>
       <c r="G24" s="22">
-        <v>0.002350084211350907</v>
+        <v>0.002385875616351201</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19382,7 +19097,7 @@
         <v>169.91304347826087</v>
       </c>
       <c r="G25" s="22">
-        <v>0.0009008656143511809</v>
+        <v>0.000914585652934627</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19403,7 +19118,7 @@
         <v>71.25</v>
       </c>
       <c r="G26" s="22">
-        <v>0.0009400336845403627</v>
+        <v>0.0009543502465404804</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19486,18 +19201,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>21282</v>
+        <v>20899</v>
       </c>
       <c r="C2" s="15">
-        <v>1760618</v>
+        <v>1751047</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>82.72803307959778</v>
+        <v>83.7861620173214</v>
       </c>
       <c r="G2" s="22">
-        <v>0.8335748697661666</v>
+        <v>0.8310402417687291</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19518,7 +19233,7 @@
         <v>55.24534803583735</v>
       </c>
       <c r="G3" s="22">
-        <v>0.05683286984450276</v>
+        <v>0.05769842532209321</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19539,7 +19254,7 @@
         <v>133.31967213114754</v>
       </c>
       <c r="G4" s="22">
-        <v>0.01911401825232071</v>
+        <v>0.019405121679656433</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19560,7 +19275,7 @@
         <v>108.32</v>
       </c>
       <c r="G5" s="22">
-        <v>0.009792017547295445</v>
+        <v>0.009941148401463337</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19581,7 +19296,7 @@
         <v>99.9020618556701</v>
       </c>
       <c r="G6" s="22">
-        <v>0.007598605616701265</v>
+        <v>0.007714331159535549</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19602,7 +19317,7 @@
         <v>91.85964912280701</v>
       </c>
       <c r="G7" s="22">
-        <v>0.006697740002350084</v>
+        <v>0.006799745506600923</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19623,7 +19338,7 @@
         <v>699.0</v>
       </c>
       <c r="G8" s="22">
-        <v>0.0008225294739728174</v>
+        <v>0.0008350564657229203</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19644,7 +19359,7 @@
         <v>60.160377358490564</v>
       </c>
       <c r="G9" s="22">
-        <v>0.008303630880106537</v>
+        <v>0.00843009384444091</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19665,7 +19380,7 @@
         <v>59.98009950248756</v>
       </c>
       <c r="G10" s="22">
-        <v>0.007872782108025538</v>
+        <v>0.007992683314776523</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19686,7 +19401,7 @@
         <v>54.99</v>
       </c>
       <c r="G11" s="22">
-        <v>0.007833614037836356</v>
+        <v>0.00795291872117067</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19707,7 +19422,7 @@
         <v>79.99152542372882</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0046218322823234495</v>
+        <v>0.004692222045490695</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19728,7 +19443,7 @@
         <v>28.64</v>
       </c>
       <c r="G13" s="22">
-        <v>0.012729622811484077</v>
+        <v>0.012923492921902337</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19749,7 +19464,7 @@
         <v>72.17525773195877</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0037993028083506326</v>
+        <v>0.0038571655797677747</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19770,7 +19485,7 @@
         <v>69.95505617977528</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0034859582468371782</v>
+        <v>0.003539048830920948</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19791,7 +19506,7 @@
         <v>28.4</v>
       </c>
       <c r="G16" s="22">
-        <v>0.008225294739728174</v>
+        <v>0.008350564657229203</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19812,7 +19527,7 @@
         <v>89.98113207547169</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0020759077200266343</v>
+        <v>0.0021075234611102273</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19833,7 +19548,7 @@
         <v>53.325581395348834</v>
       </c>
       <c r="G18" s="22">
-        <v>0.003368454036269633</v>
+        <v>0.003419755050103388</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19854,7 +19569,7 @@
         <v>74.98333333333333</v>
       </c>
       <c r="G19" s="22">
-        <v>0.002350084211350907</v>
+        <v>0.002385875616351201</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19875,7 +19590,7 @@
         <v>169.91304347826087</v>
       </c>
       <c r="G20" s="22">
-        <v>0.0009008656143511809</v>
+        <v>0.000914585652934627</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
